--- a/Python/Data.xlsx
+++ b/Python/Data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\brend\Desktop\Turbopump_Mark2\Python\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DE9BC90-3485-4252-A82B-6647F9AE1385}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{623C85C6-E918-4CD3-8912-C2AB9E9A3A7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{E71AA300-BBD3-4BC5-B02A-D6A9C48800E7}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" activeTab="5" xr2:uid="{E71AA300-BBD3-4BC5-B02A-D6A9C48800E7}"/>
   </bookViews>
   <sheets>
     <sheet name="Expansion Loss" sheetId="2" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="Incidence Loss" sheetId="3" r:id="rId3"/>
     <sheet name="Mach Loss" sheetId="4" r:id="rId4"/>
     <sheet name="Pitch Chord Zweifel" sheetId="5" r:id="rId5"/>
+    <sheet name="Diffuser Length &amp; Area" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,10 +40,24 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+  <si>
+    <t>L/R1</t>
+  </si>
+  <si>
+    <t>AR</t>
+  </si>
+  <si>
+    <t>cp</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="175" formatCode="0.000"/>
+    <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -73,9 +88,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="175" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4434,4 +4450,3614 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B36A080-8CFB-4D64-936C-02AD66BE7DAC}">
+  <dimension ref="A1:C327"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="3" width="8.88671875" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="2">
+        <v>8.1911827150194298</v>
+      </c>
+      <c r="B2" s="2">
+        <v>10.012929704599699</v>
+      </c>
+      <c r="C2" s="2">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="2">
+        <v>7.4922569017766198</v>
+      </c>
+      <c r="B3" s="2">
+        <v>8.94250177022505</v>
+      </c>
+      <c r="C3" s="2">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
+        <v>6.7662070842326703</v>
+      </c>
+      <c r="B4" s="2">
+        <v>7.9865074728071201</v>
+      </c>
+      <c r="C4" s="2">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="2">
+        <v>6.0717125060251798</v>
+      </c>
+      <c r="B5" s="2">
+        <v>6.9700184318281497</v>
+      </c>
+      <c r="C5" s="2">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="2">
+        <v>5.32836081104647</v>
+      </c>
+      <c r="B6" s="2">
+        <v>5.95788603735331</v>
+      </c>
+      <c r="C6" s="2">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="2">
+        <v>4.55836615773294</v>
+      </c>
+      <c r="B7" s="2">
+        <v>4.99958299541077</v>
+      </c>
+      <c r="C7" s="2">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="2">
+        <v>4.0130538637602502</v>
+      </c>
+      <c r="B8" s="2">
+        <v>4.3532010188191297</v>
+      </c>
+      <c r="C8" s="2">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="2">
+        <v>3.70587786608414</v>
+      </c>
+      <c r="B9" s="2">
+        <v>3.9877646335043102</v>
+      </c>
+      <c r="C9" s="2">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="2">
+        <v>3.0128186905377001</v>
+      </c>
+      <c r="B10" s="2">
+        <v>3.23997699975813</v>
+      </c>
+      <c r="C10" s="2">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="2">
+        <v>2.75574509973913</v>
+      </c>
+      <c r="B11" s="2">
+        <v>3.0093675140373999</v>
+      </c>
+      <c r="C11" s="2">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="2">
+        <v>2.3801519984467698</v>
+      </c>
+      <c r="B12" s="2">
+        <v>2.6263478889118299</v>
+      </c>
+      <c r="C12" s="2">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="2">
+        <v>1.99765341321651</v>
+      </c>
+      <c r="B13" s="2">
+        <v>2.26578582365901</v>
+      </c>
+      <c r="C13" s="2">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="2">
+        <v>1.70897505566959</v>
+      </c>
+      <c r="B14" s="2">
+        <v>1.9957411714951201</v>
+      </c>
+      <c r="C14" s="2">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" s="2">
+        <v>1.54336393960364</v>
+      </c>
+      <c r="B15" s="2">
+        <v>1.84090452414242</v>
+      </c>
+      <c r="C15" s="2">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" s="2">
+        <v>1.38054608108378</v>
+      </c>
+      <c r="B16" s="2">
+        <v>1.6670231794719099</v>
+      </c>
+      <c r="C16" s="2">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" s="2">
+        <v>1.2789406058847901</v>
+      </c>
+      <c r="B17" s="2">
+        <v>1.5412417723477401</v>
+      </c>
+      <c r="C17" s="2">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" s="2">
+        <v>1.2427969451509799</v>
+      </c>
+      <c r="B18" s="2">
+        <v>1.4649571299754001</v>
+      </c>
+      <c r="C18" s="2">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" s="2">
+        <v>1.2912205897462301</v>
+      </c>
+      <c r="B19" s="2">
+        <v>1.37647598496902</v>
+      </c>
+      <c r="C19" s="2">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" s="2">
+        <v>1.3761556325275099</v>
+      </c>
+      <c r="B20" s="2">
+        <v>1.29932121745743</v>
+      </c>
+      <c r="C20" s="2">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" s="2">
+        <v>1.4949779741787499</v>
+      </c>
+      <c r="B21" s="2">
+        <v>1.2696841175073399</v>
+      </c>
+      <c r="C21" s="2">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" s="2">
+        <v>1.6819727152033099</v>
+      </c>
+      <c r="B22" s="2">
+        <v>1.2638383176045</v>
+      </c>
+      <c r="C22" s="2">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" s="2">
+        <v>1.98496763846765</v>
+      </c>
+      <c r="B23" s="2">
+        <v>1.2609255184857999</v>
+      </c>
+      <c r="C23" s="2">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" s="2">
+        <v>2.4571872152138199</v>
+      </c>
+      <c r="B24" s="2">
+        <v>1.2755569567680101</v>
+      </c>
+      <c r="C24" s="2">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" s="2">
+        <v>3.0032372461720298</v>
+      </c>
+      <c r="B25" s="2">
+        <v>1.2873842542163201</v>
+      </c>
+      <c r="C25" s="2">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" s="2">
+        <v>4.0002914454797098</v>
+      </c>
+      <c r="B26" s="2">
+        <v>1.3113688633412299</v>
+      </c>
+      <c r="C26" s="2">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" s="2">
+        <v>4.9994993489099802</v>
+      </c>
+      <c r="B27" s="2">
+        <v>1.33272166596399</v>
+      </c>
+      <c r="C27" s="2">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" s="2">
+        <v>5.9567732259328201</v>
+      </c>
+      <c r="B28" s="2">
+        <v>1.35130058284364</v>
+      </c>
+      <c r="C28" s="2">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" s="2">
+        <v>6.9851999173646799</v>
+      </c>
+      <c r="B29" s="2">
+        <v>1.37330358706014</v>
+      </c>
+      <c r="C29" s="2">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" s="2">
+        <v>7.9850891610622696</v>
+      </c>
+      <c r="B30" s="2">
+        <v>1.3860372168089401</v>
+      </c>
+      <c r="C30" s="2">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" s="2">
+        <v>9.0412948617335207</v>
+      </c>
+      <c r="B31" s="2">
+        <v>1.3988889161004801</v>
+      </c>
+      <c r="C31" s="2">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" s="2">
+        <v>9.9478973911185999</v>
+      </c>
+      <c r="B32" s="2">
+        <v>1.4118597797064301</v>
+      </c>
+      <c r="C32" s="2">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" s="2">
+        <v>11.335713766434599</v>
+      </c>
+      <c r="B33" s="2">
+        <v>1.43816342979734</v>
+      </c>
+      <c r="C33" s="2">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" s="2">
+        <v>13.0411686630408</v>
+      </c>
+      <c r="B34" s="2">
+        <v>1.4582122663278201</v>
+      </c>
+      <c r="C34" s="2">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" s="2">
+        <v>14.9554951667018</v>
+      </c>
+      <c r="B35" s="2">
+        <v>1.4785405953262001</v>
+      </c>
+      <c r="C35" s="2">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" s="2">
+        <v>17.205545140506299</v>
+      </c>
+      <c r="B36" s="2">
+        <v>1.50608654218556</v>
+      </c>
+      <c r="C36" s="2">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" s="2">
+        <v>19.984171327016998</v>
+      </c>
+      <c r="B37" s="2">
+        <v>1.5306099006143601</v>
+      </c>
+      <c r="C37" s="2">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" s="2">
+        <v>23.211534442309102</v>
+      </c>
+      <c r="B38" s="2">
+        <v>1.56272758105872</v>
+      </c>
+      <c r="C38" s="2">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" s="2">
+        <v>26.36562494871</v>
+      </c>
+      <c r="B39" s="2">
+        <v>1.59184197334499</v>
+      </c>
+      <c r="C39" s="2">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" s="2">
+        <v>29.853065453241999</v>
+      </c>
+      <c r="B40" s="2">
+        <v>1.6214987812438399</v>
+      </c>
+      <c r="C40" s="2">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41" s="2">
+        <v>33.480329999114197</v>
+      </c>
+      <c r="B41" s="2">
+        <v>1.6441034194414099</v>
+      </c>
+      <c r="C41" s="2">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42" s="2">
+        <v>37.072946539600203</v>
+      </c>
+      <c r="B42" s="2">
+        <v>1.6670231794719099</v>
+      </c>
+      <c r="C42" s="2">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" s="2">
+        <v>40.145880875703398</v>
+      </c>
+      <c r="B43" s="2">
+        <v>1.6902624543173801</v>
+      </c>
+      <c r="C43" s="2">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44" s="2">
+        <v>44.453746290119902</v>
+      </c>
+      <c r="B44" s="2">
+        <v>1.7098758021468199</v>
+      </c>
+      <c r="C44" s="2">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45" s="2">
+        <v>50.014106990189099</v>
+      </c>
+      <c r="B45" s="2">
+        <v>1.73371246753158</v>
+      </c>
+      <c r="C45" s="2">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A46" s="2">
+        <v>9.5140257057284199</v>
+      </c>
+      <c r="B46" s="2">
+        <v>9.9898526603189506</v>
+      </c>
+      <c r="C46" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A47" s="2">
+        <v>8.67455114485597</v>
+      </c>
+      <c r="B47" s="2">
+        <v>8.94250177022505</v>
+      </c>
+      <c r="C47" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A48" s="2">
+        <v>7.8339291055202702</v>
+      </c>
+      <c r="B48" s="2">
+        <v>8.0049566925169202</v>
+      </c>
+      <c r="C48" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A49" s="2">
+        <v>7.0522696013355004</v>
+      </c>
+      <c r="B49" s="2">
+        <v>6.9700184318281497</v>
+      </c>
+      <c r="C49" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A50" s="2">
+        <v>6.1888696039875599</v>
+      </c>
+      <c r="B50" s="2">
+        <v>5.9992705077698103</v>
+      </c>
+      <c r="C50" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A51" s="2">
+        <v>5.2776861352496498</v>
+      </c>
+      <c r="B51" s="2">
+        <v>4.99958299541077</v>
+      </c>
+      <c r="C51" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A52" s="2">
+        <v>4.3318710496016504</v>
+      </c>
+      <c r="B52" s="2">
+        <v>3.96940441793127</v>
+      </c>
+      <c r="C52" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A53" s="2">
+        <v>4.0130538637602502</v>
+      </c>
+      <c r="B53" s="2">
+        <v>3.6194449475173398</v>
+      </c>
+      <c r="C53" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A54" s="2">
+        <v>3.37888797867982</v>
+      </c>
+      <c r="B54" s="2">
+        <v>2.9955119730578699</v>
+      </c>
+      <c r="C54" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A55" s="2">
+        <v>3.0032372461720298</v>
+      </c>
+      <c r="B55" s="2">
+        <v>2.6445909395225198</v>
+      </c>
+      <c r="C55" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A56" s="2">
+        <v>2.5692432461053598</v>
+      </c>
+      <c r="B56" s="2">
+        <v>2.28679478194063</v>
+      </c>
+      <c r="C56" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A57" s="2">
+        <v>2.2120121932724399</v>
+      </c>
+      <c r="B57" s="2">
+        <v>1.9911415379466699</v>
+      </c>
+      <c r="C57" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A58" s="2">
+        <v>1.9913004238711001</v>
+      </c>
+      <c r="B58" s="2">
+        <v>1.8030696615908099</v>
+      </c>
+      <c r="C58" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A59" s="2">
+        <v>1.8098230794567001</v>
+      </c>
+      <c r="B59" s="2">
+        <v>1.6441034194414099</v>
+      </c>
+      <c r="C59" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A60" s="2">
+        <v>1.70897505566959</v>
+      </c>
+      <c r="B60" s="2">
+        <v>1.5270822664957699</v>
+      </c>
+      <c r="C60" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A61" s="2">
+        <v>1.66067835265583</v>
+      </c>
+      <c r="B61" s="2">
+        <v>1.4582122663278201</v>
+      </c>
+      <c r="C61" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A62" s="2">
+        <v>1.69272207281765</v>
+      </c>
+      <c r="B62" s="2">
+        <v>1.4021204173606501</v>
+      </c>
+      <c r="C62" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A63" s="2">
+        <v>1.7755626032498899</v>
+      </c>
+      <c r="B63" s="2">
+        <v>1.36383019498723</v>
+      </c>
+      <c r="C63" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A64" s="2">
+        <v>1.8983944440642</v>
+      </c>
+      <c r="B64" s="2">
+        <v>1.3388860812035801</v>
+      </c>
+      <c r="C64" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A65" s="2">
+        <v>2.0623088065749999</v>
+      </c>
+      <c r="B65" s="2">
+        <v>1.3265856325380501</v>
+      </c>
+      <c r="C65" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A66" s="2">
+        <v>2.2981997983396201</v>
+      </c>
+      <c r="B66" s="2">
+        <v>1.32047785025199</v>
+      </c>
+      <c r="C66" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A67" s="2">
+        <v>2.5939123084942701</v>
+      </c>
+      <c r="B67" s="2">
+        <v>1.3265856325380501</v>
+      </c>
+      <c r="C67" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A68" s="2">
+        <v>3.0224307032762998</v>
+      </c>
+      <c r="B68" s="2">
+        <v>1.33272166596399</v>
+      </c>
+      <c r="C68" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A69" s="2">
+        <v>3.4882479557060999</v>
+      </c>
+      <c r="B69" s="2">
+        <v>1.34507900953499</v>
+      </c>
+      <c r="C69" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A70" s="2">
+        <v>4.0130538637602502</v>
+      </c>
+      <c r="B70" s="2">
+        <v>1.35755093362496</v>
+      </c>
+      <c r="C70" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A71" s="2">
+        <v>4.54386952311107</v>
+      </c>
+      <c r="B71" s="2">
+        <v>1.37647598496902</v>
+      </c>
+      <c r="C71" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A72" s="2">
+        <v>5.0314507628112501</v>
+      </c>
+      <c r="B72" s="2">
+        <v>1.3860372168089401</v>
+      </c>
+      <c r="C72" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A73" s="2">
+        <v>6.0139682815469104</v>
+      </c>
+      <c r="B73" s="2">
+        <v>1.4021204173606501</v>
+      </c>
+      <c r="C73" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A74" s="2">
+        <v>7.0074853044004897</v>
+      </c>
+      <c r="B74" s="2">
+        <v>1.4249509125494499</v>
+      </c>
+      <c r="C74" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A75" s="2">
+        <v>8.0361212486810594</v>
+      </c>
+      <c r="B75" s="2">
+        <v>1.4414856570894601</v>
+      </c>
+      <c r="C75" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A76" s="2">
+        <v>9.0412948617335207</v>
+      </c>
+      <c r="B76" s="2">
+        <v>1.4649571299754001</v>
+      </c>
+      <c r="C76" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A77" s="2">
+        <v>10.0434139607357</v>
+      </c>
+      <c r="B77" s="2">
+        <v>1.4751329666105399</v>
+      </c>
+      <c r="C77" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A78" s="2">
+        <v>11.408159436918901</v>
+      </c>
+      <c r="B78" s="2">
+        <v>1.4956971800340999</v>
+      </c>
+      <c r="C78" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A79" s="2">
+        <v>12.8760629089203</v>
+      </c>
+      <c r="B79" s="2">
+        <v>1.51654807057986</v>
+      </c>
+      <c r="C79" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A80" s="2">
+        <v>14.813262893808</v>
+      </c>
+      <c r="B80" s="2">
+        <v>1.5412417723477401</v>
+      </c>
+      <c r="C80" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A81" s="2">
+        <v>6.32841309780071</v>
+      </c>
+      <c r="B81" s="2">
+        <v>2.2294835118458001</v>
+      </c>
+      <c r="C81" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A82" s="2">
+        <v>17.205545140506299</v>
+      </c>
+      <c r="B82" s="2">
+        <v>1.5555325688383099</v>
+      </c>
+      <c r="C82" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A83" s="2">
+        <v>19.8572650807583</v>
+      </c>
+      <c r="B83" s="2">
+        <v>1.59551920552808</v>
+      </c>
+      <c r="C83" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A84" s="2">
+        <v>23.584171733087199</v>
+      </c>
+      <c r="B84" s="2">
+        <v>1.6252445220919201</v>
+      </c>
+      <c r="C84" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A85" s="2">
+        <v>27.218966094337802</v>
+      </c>
+      <c r="B85" s="2">
+        <v>1.6593479760049901</v>
+      </c>
+      <c r="C85" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A86" s="2">
+        <v>30.043854087053099</v>
+      </c>
+      <c r="B86" s="2">
+        <v>1.68636686504879</v>
+      </c>
+      <c r="C86" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A87" s="2">
+        <v>34.563943348428602</v>
+      </c>
+      <c r="B87" s="2">
+        <v>1.7177847187058699</v>
+      </c>
+      <c r="C87" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A88" s="2">
+        <v>39.7640787474135</v>
+      </c>
+      <c r="B88" s="2">
+        <v>1.75382999754893</v>
+      </c>
+      <c r="C88" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A89" s="2">
+        <v>45.023762867129903</v>
+      </c>
+      <c r="B89" s="2">
+        <v>1.78650472292715</v>
+      </c>
+      <c r="C89" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A90" s="2">
+        <v>50.173670602499797</v>
+      </c>
+      <c r="B90" s="2">
+        <v>1.81559408428053</v>
+      </c>
+      <c r="C90" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A91" s="2">
+        <v>11.0857577222591</v>
+      </c>
+      <c r="B91" s="2">
+        <v>9.9438580078649501</v>
+      </c>
+      <c r="C91" s="2">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A92" s="2">
+        <v>10.1076006430504</v>
+      </c>
+      <c r="B92" s="2">
+        <v>8.94250177022505</v>
+      </c>
+      <c r="C92" s="2">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A93" s="2">
+        <v>9.2451533939585708</v>
+      </c>
+      <c r="B93" s="2">
+        <v>7.9865074728071201</v>
+      </c>
+      <c r="C93" s="2">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A94" s="2">
+        <v>8.4294029087650202</v>
+      </c>
+      <c r="B94" s="2">
+        <v>6.9700184318281497</v>
+      </c>
+      <c r="C94" s="2">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A95" s="2">
+        <v>7.4684298314974997</v>
+      </c>
+      <c r="B95" s="2">
+        <v>5.9992705077698103</v>
+      </c>
+      <c r="C95" s="2">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A96" s="2">
+        <v>6.9629854028963702</v>
+      </c>
+      <c r="B96" s="2">
+        <v>5.5338259174329201</v>
+      </c>
+      <c r="C96" s="2">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A97" s="2">
+        <v>6.3688574967524003</v>
+      </c>
+      <c r="B97" s="2">
+        <v>4.98806033405448</v>
+      </c>
+      <c r="C97" s="2">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A98" s="2">
+        <v>5.9757775491297203</v>
+      </c>
+      <c r="B98" s="2">
+        <v>4.59046480334072</v>
+      </c>
+      <c r="C98" s="2">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A99" s="2">
+        <v>5.2945239179286103</v>
+      </c>
+      <c r="B99" s="2">
+        <v>3.9877646335043102</v>
+      </c>
+      <c r="C99" s="2">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A100" s="2">
+        <v>4.9994993489099802</v>
+      </c>
+      <c r="B100" s="2">
+        <v>3.7039304114168199</v>
+      </c>
+      <c r="C100" s="2">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A101" s="2">
+        <v>4.4863425465323301</v>
+      </c>
+      <c r="B101" s="2">
+        <v>3.2624824205493299</v>
+      </c>
+      <c r="C101" s="2">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A102" s="2">
+        <v>4.1827182377951004</v>
+      </c>
+      <c r="B102" s="2">
+        <v>3.00243175103622</v>
+      </c>
+      <c r="C102" s="2">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A103" s="2">
+        <v>3.6126364421622901</v>
+      </c>
+      <c r="B103" s="2">
+        <v>2.5311559471598901</v>
+      </c>
+      <c r="C103" s="2">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A104" s="2">
+        <v>2.9652152127834799</v>
+      </c>
+      <c r="B104" s="2">
+        <v>2.0423259714138799</v>
+      </c>
+      <c r="C104" s="2">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A105" s="2">
+        <v>2.7645369520620799</v>
+      </c>
+      <c r="B105" s="2">
+        <v>1.91013742795844</v>
+      </c>
+      <c r="C105" s="2">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A106" s="2">
+        <v>2.5206067257173399</v>
+      </c>
+      <c r="B106" s="2">
+        <v>1.74575512357996</v>
+      </c>
+      <c r="C106" s="2">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A107" s="2">
+        <v>2.35001844210848</v>
+      </c>
+      <c r="B107" s="2">
+        <v>1.62899891578306</v>
+      </c>
+      <c r="C107" s="2">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A108" s="2">
+        <v>2.26188752262299</v>
+      </c>
+      <c r="B108" s="2">
+        <v>1.53414568373891</v>
+      </c>
+      <c r="C108" s="2">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A109" s="2">
+        <v>2.2763430709468802</v>
+      </c>
+      <c r="B109" s="2">
+        <v>1.4683412520147701</v>
+      </c>
+      <c r="C109" s="2">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A110" s="2">
+        <v>2.4260783661017999</v>
+      </c>
+      <c r="B110" s="2">
+        <v>1.4282426182857599</v>
+      </c>
+      <c r="C110" s="2">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A111" s="2">
+        <v>2.5939123084942701</v>
+      </c>
+      <c r="B111" s="2">
+        <v>1.4151212442907899</v>
+      </c>
+      <c r="C111" s="2">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A112" s="2">
+        <v>2.9652152127834799</v>
+      </c>
+      <c r="B112" s="2">
+        <v>1.4118597797064301</v>
+      </c>
+      <c r="C112" s="2">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A113" s="2">
+        <v>3.4440855171879901</v>
+      </c>
+      <c r="B113" s="2">
+        <v>1.4216667932879601</v>
+      </c>
+      <c r="C113" s="2">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A114" s="2">
+        <v>3.9748882419653402</v>
+      </c>
+      <c r="B114" s="2">
+        <v>1.43816342979734</v>
+      </c>
+      <c r="C114" s="2">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A115" s="2">
+        <v>4.9994993489099802</v>
+      </c>
+      <c r="B115" s="2">
+        <v>1.4582122663278201</v>
+      </c>
+      <c r="C115" s="2">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A116" s="2">
+        <v>5.9948425031894104</v>
+      </c>
+      <c r="B116" s="2">
+        <v>1.4819560958295099</v>
+      </c>
+      <c r="C116" s="2">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A117" s="2">
+        <v>6.9187680908159601</v>
+      </c>
+      <c r="B117" s="2">
+        <v>1.50608654218556</v>
+      </c>
+      <c r="C117" s="2">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A118" s="2">
+        <v>7.9596947728131697</v>
+      </c>
+      <c r="B118" s="2">
+        <v>1.5200513701948499</v>
+      </c>
+      <c r="C118" s="2">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A119" s="2">
+        <v>8.9838795817379609</v>
+      </c>
+      <c r="B119" s="2">
+        <v>1.53414568373891</v>
+      </c>
+      <c r="C119" s="2">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A120" s="2">
+        <v>9.9478973911185999</v>
+      </c>
+      <c r="B120" s="2">
+        <v>1.5555325688383099</v>
+      </c>
+      <c r="C120" s="2">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A121" s="2">
+        <v>11.852660576235801</v>
+      </c>
+      <c r="B121" s="2">
+        <v>1.5735825475589</v>
+      </c>
+      <c r="C121" s="2">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A122" s="2">
+        <v>14.3946308276034</v>
+      </c>
+      <c r="B122" s="2">
+        <v>1.6103132765635899</v>
+      </c>
+      <c r="C122" s="2">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A123" s="2">
+        <v>16.933692145197401</v>
+      </c>
+      <c r="B123" s="2">
+        <v>1.64031421403081</v>
+      </c>
+      <c r="C123" s="2">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A124" s="2">
+        <v>19.984171327016998</v>
+      </c>
+      <c r="B124" s="2">
+        <v>1.67087408388841</v>
+      </c>
+      <c r="C124" s="2">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A125" s="2">
+        <v>23.064133348824999</v>
+      </c>
+      <c r="B125" s="2">
+        <v>1.7020032993248699</v>
+      </c>
+      <c r="C125" s="2">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A126" s="2">
+        <v>26.114878134851899</v>
+      </c>
+      <c r="B126" s="2">
+        <v>1.7377174274387801</v>
+      </c>
+      <c r="C126" s="2">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A127" s="2">
+        <v>30.043854087053099</v>
+      </c>
+      <c r="B127" s="2">
+        <v>1.7782794100389201</v>
+      </c>
+      <c r="C127" s="2">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A128" s="2">
+        <v>35.007146055054498</v>
+      </c>
+      <c r="B128" s="2">
+        <v>1.8114096401353099</v>
+      </c>
+      <c r="C128" s="2">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A129" s="2">
+        <v>39.7640787474135</v>
+      </c>
+      <c r="B129" s="2">
+        <v>1.84090452414242</v>
+      </c>
+      <c r="C129" s="2">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A130" s="2">
+        <v>44.595570282702397</v>
+      </c>
+      <c r="B130" s="2">
+        <v>1.8708796684745901</v>
+      </c>
+      <c r="C130" s="2">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A131" s="2">
+        <v>50.014106990189099</v>
+      </c>
+      <c r="B131" s="2">
+        <v>1.9013428931313801</v>
+      </c>
+      <c r="C131" s="2">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A132" s="2">
+        <v>12.4723857730662</v>
+      </c>
+      <c r="B132" s="2">
+        <v>9.9898526603189506</v>
+      </c>
+      <c r="C132" s="2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A133" s="2">
+        <v>11.517696981609699</v>
+      </c>
+      <c r="B133" s="2">
+        <v>8.9631593831398106</v>
+      </c>
+      <c r="C133" s="2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A134" s="2">
+        <v>10.738208400874999</v>
+      </c>
+      <c r="B134" s="2">
+        <v>7.9865074728071201</v>
+      </c>
+      <c r="C134" s="2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A135" s="2">
+        <v>9.8219535326262193</v>
+      </c>
+      <c r="B135" s="2">
+        <v>6.9700184318281497</v>
+      </c>
+      <c r="C135" s="2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A136" s="2">
+        <v>8.7299895307210296</v>
+      </c>
+      <c r="B136" s="2">
+        <v>5.9992705077698103</v>
+      </c>
+      <c r="C136" s="2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A137" s="2">
+        <v>8.0105645668595198</v>
+      </c>
+      <c r="B137" s="2">
+        <v>5.2842554782858997</v>
+      </c>
+      <c r="C137" s="2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A138" s="2">
+        <v>7.4684298314974997</v>
+      </c>
+      <c r="B138" s="2">
+        <v>4.7741064187469</v>
+      </c>
+      <c r="C138" s="2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A139" s="2">
+        <v>7.0074853044004897</v>
+      </c>
+      <c r="B139" s="2">
+        <v>4.37333645998942</v>
+      </c>
+      <c r="C139" s="2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A140" s="2">
+        <v>6.5540798900989001</v>
+      </c>
+      <c r="B140" s="2">
+        <v>3.9969765632652199</v>
+      </c>
+      <c r="C140" s="2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A141" s="2">
+        <v>6.0139682815469104</v>
+      </c>
+      <c r="B141" s="2">
+        <v>3.5532462030282002</v>
+      </c>
+      <c r="C141" s="2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A142" s="2">
+        <v>5.5183664370783996</v>
+      </c>
+      <c r="B142" s="2">
+        <v>3.1514971243712102</v>
+      </c>
+      <c r="C142" s="2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A143" s="2">
+        <v>5.0959674926835703</v>
+      </c>
+      <c r="B143" s="2">
+        <v>2.82108951671455</v>
+      </c>
+      <c r="C143" s="2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A144" s="2">
+        <v>4.6611458865738697</v>
+      </c>
+      <c r="B144" s="2">
+        <v>2.5546254865765801</v>
+      </c>
+      <c r="C144" s="2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A145" s="2">
+        <v>4.2906733588264503</v>
+      </c>
+      <c r="B145" s="2">
+        <v>2.3293989064000602</v>
+      </c>
+      <c r="C145" s="2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A146" s="2">
+        <v>3.9748882419653402</v>
+      </c>
+      <c r="B146" s="2">
+        <v>2.1536394593758499</v>
+      </c>
+      <c r="C146" s="2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A147" s="2">
+        <v>3.6823442883649702</v>
+      </c>
+      <c r="B147" s="2">
+        <v>2.0003514304202099</v>
+      </c>
+      <c r="C147" s="2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A148" s="2">
+        <v>3.4440855171879901</v>
+      </c>
+      <c r="B148" s="2">
+        <v>1.84090452414242</v>
+      </c>
+      <c r="C148" s="2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A149" s="2">
+        <v>3.2938737559263198</v>
+      </c>
+      <c r="B149" s="2">
+        <v>1.7217528847405801</v>
+      </c>
+      <c r="C149" s="2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A150" s="2">
+        <v>3.31492464849961</v>
+      </c>
+      <c r="B150" s="2">
+        <v>1.67087408388841</v>
+      </c>
+      <c r="C150" s="2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A151" s="2">
+        <v>3.4331325468425802</v>
+      </c>
+      <c r="B151" s="2">
+        <v>1.6103132765635899</v>
+      </c>
+      <c r="C151" s="2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A152" s="2">
+        <v>3.6357245224244599</v>
+      </c>
+      <c r="B152" s="2">
+        <v>1.5772175995826201</v>
+      </c>
+      <c r="C152" s="2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A153" s="2">
+        <v>4.0002914454797098</v>
+      </c>
+      <c r="B153" s="2">
+        <v>1.5772175995826201</v>
+      </c>
+      <c r="C153" s="2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A154" s="2">
+        <v>4.5874983235069102</v>
+      </c>
+      <c r="B154" s="2">
+        <v>1.5735825475589</v>
+      </c>
+      <c r="C154" s="2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A155" s="2">
+        <v>5.0314507628112501</v>
+      </c>
+      <c r="B155" s="2">
+        <v>1.5772175995826201</v>
+      </c>
+      <c r="C155" s="2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A156" s="2">
+        <v>5.9948425031894104</v>
+      </c>
+      <c r="B156" s="2">
+        <v>1.5845129144674199</v>
+      </c>
+      <c r="C156" s="2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A157" s="2">
+        <v>7.0074853044004897</v>
+      </c>
+      <c r="B157" s="2">
+        <v>1.5992049322959101</v>
+      </c>
+      <c r="C157" s="2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A158" s="2">
+        <v>8.0617594658276293</v>
+      </c>
+      <c r="B158" s="2">
+        <v>1.6103132765635899</v>
+      </c>
+      <c r="C158" s="2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A159" s="2">
+        <v>9.0701399567461696</v>
+      </c>
+      <c r="B159" s="2">
+        <v>1.61403317835321</v>
+      </c>
+      <c r="C159" s="2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A160" s="2">
+        <v>9.9796348855606105</v>
+      </c>
+      <c r="B160" s="2">
+        <v>1.62899891578306</v>
+      </c>
+      <c r="C160" s="2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A161" s="2">
+        <v>11.481068102083499</v>
+      </c>
+      <c r="B161" s="2">
+        <v>1.65170811022801</v>
+      </c>
+      <c r="C161" s="2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A162" s="2">
+        <v>13.2083915169483</v>
+      </c>
+      <c r="B162" s="2">
+        <v>1.6786026005991299</v>
+      </c>
+      <c r="C162" s="2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A163" s="2">
+        <v>15.292704088654601</v>
+      </c>
+      <c r="B163" s="2">
+        <v>1.7020032993248699</v>
+      </c>
+      <c r="C163" s="2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A164" s="2">
+        <v>17.649616818887701</v>
+      </c>
+      <c r="B164" s="2">
+        <v>1.72573021743134</v>
+      </c>
+      <c r="C164" s="2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A165" s="2">
+        <v>19.984171327016998</v>
+      </c>
+      <c r="B165" s="2">
+        <v>1.74575512357996</v>
+      </c>
+      <c r="C165" s="2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A166" s="2">
+        <v>23.434404266786601</v>
+      </c>
+      <c r="B166" s="2">
+        <v>1.79891408278925</v>
+      </c>
+      <c r="C166" s="2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A167" s="2">
+        <v>27.132403630375698</v>
+      </c>
+      <c r="B167" s="2">
+        <v>1.8366617464066699</v>
+      </c>
+      <c r="C167" s="2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A168" s="2">
+        <v>29.758125957983498</v>
+      </c>
+      <c r="B168" s="2">
+        <v>1.8752014912703301</v>
+      </c>
+      <c r="C168" s="2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A169" s="2">
+        <v>34.784838838739297</v>
+      </c>
+      <c r="B169" s="2">
+        <v>1.92784872137245</v>
+      </c>
+      <c r="C169" s="2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A170" s="2">
+        <v>40.0182079011133</v>
+      </c>
+      <c r="B170" s="2">
+        <v>1.9728487685937399</v>
+      </c>
+      <c r="C170" s="2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A171" s="2">
+        <v>45.167405424704903</v>
+      </c>
+      <c r="B171" s="2">
+        <v>2.0049723392670802</v>
+      </c>
+      <c r="C171" s="2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A172" s="2">
+        <v>50.3337432821099</v>
+      </c>
+      <c r="B172" s="2">
+        <v>2.0565123083486498</v>
+      </c>
+      <c r="C172" s="2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A173" s="2">
+        <v>14.532843527584101</v>
+      </c>
+      <c r="B173" s="2">
+        <v>10.012929704599699</v>
+      </c>
+      <c r="C173" s="2">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A174" s="2">
+        <v>13.592524760669701</v>
+      </c>
+      <c r="B174" s="2">
+        <v>8.9631593831398106</v>
+      </c>
+      <c r="C174" s="2">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A175" s="2">
+        <v>12.5520958264855</v>
+      </c>
+      <c r="B175" s="2">
+        <v>8.0049566925169202</v>
+      </c>
+      <c r="C175" s="2">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A176" s="2">
+        <v>11.554442720891799</v>
+      </c>
+      <c r="B176" s="2">
+        <v>6.9861195125405802</v>
+      </c>
+      <c r="C176" s="2">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A177" s="2">
+        <v>10.468030624421401</v>
+      </c>
+      <c r="B177" s="2">
+        <v>5.9854438421240399</v>
+      </c>
+      <c r="C177" s="2">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A178" s="2">
+        <v>9.2746488735478891</v>
+      </c>
+      <c r="B178" s="2">
+        <v>5.0227082333322102</v>
+      </c>
+      <c r="C178" s="2">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A179" s="2">
+        <v>8.6469641116724993</v>
+      </c>
+      <c r="B179" s="2">
+        <v>4.4961200925723297</v>
+      </c>
+      <c r="C179" s="2">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A180" s="2">
+        <v>7.9596947728131697</v>
+      </c>
+      <c r="B180" s="2">
+        <v>4.0247402293207397</v>
+      </c>
+      <c r="C180" s="2">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A181" s="2">
+        <v>7.4922569017766198</v>
+      </c>
+      <c r="B181" s="2">
+        <v>3.6111031241160201</v>
+      </c>
+      <c r="C181" s="2">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A182" s="2">
+        <v>7.0074853044004897</v>
+      </c>
+      <c r="B182" s="2">
+        <v>3.30033938314009</v>
+      </c>
+      <c r="C182" s="2">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A183" s="2">
+        <v>6.5749898438214096</v>
+      </c>
+      <c r="B183" s="2">
+        <v>2.9886081432612799</v>
+      </c>
+      <c r="C183" s="2">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A184" s="2">
+        <v>6.0139682815469104</v>
+      </c>
+      <c r="B184" s="2">
+        <v>2.6082306834330402</v>
+      </c>
+      <c r="C184" s="2">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A185" s="2">
+        <v>5.5536338904341802</v>
+      </c>
+      <c r="B185" s="2">
+        <v>2.34557929983588</v>
+      </c>
+      <c r="C185" s="2">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A186" s="2">
+        <v>5.2776861352496498</v>
+      </c>
+      <c r="B186" s="2">
+        <v>2.1536394593758499</v>
+      </c>
+      <c r="C186" s="2">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A187" s="2">
+        <v>5.07976116431281</v>
+      </c>
+      <c r="B187" s="2">
+        <v>2.0376189727363099</v>
+      </c>
+      <c r="C187" s="2">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A188" s="2">
+        <v>4.9994993489099802</v>
+      </c>
+      <c r="B188" s="2">
+        <v>1.9234055612163099</v>
+      </c>
+      <c r="C188" s="2">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A189" s="2">
+        <v>5.1285354270351604</v>
+      </c>
+      <c r="B189" s="2">
+        <v>1.8579738719794101</v>
+      </c>
+      <c r="C189" s="2">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A190" s="2">
+        <v>5.4485019889105804</v>
+      </c>
+      <c r="B190" s="2">
+        <v>1.79891408278925</v>
+      </c>
+      <c r="C190" s="2">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A191" s="2">
+        <v>5.9378293407788796</v>
+      </c>
+      <c r="B191" s="2">
+        <v>1.7700919676199001</v>
+      </c>
+      <c r="C191" s="2">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A192" s="2">
+        <v>6.5749898438214096</v>
+      </c>
+      <c r="B192" s="2">
+        <v>1.75382999754893</v>
+      </c>
+      <c r="C192" s="2">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A193" s="2">
+        <v>6.9629854028963702</v>
+      </c>
+      <c r="B193" s="2">
+        <v>1.7619422213092599</v>
+      </c>
+      <c r="C193" s="2">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A194" s="2">
+        <v>8.0105645668595198</v>
+      </c>
+      <c r="B194" s="2">
+        <v>1.7619422213092599</v>
+      </c>
+      <c r="C194" s="2">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A195" s="2">
+        <v>9.01254150064233</v>
+      </c>
+      <c r="B195" s="2">
+        <v>1.7782794100389201</v>
+      </c>
+      <c r="C195" s="2">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A196" s="2">
+        <v>9.9796348855606105</v>
+      </c>
+      <c r="B196" s="2">
+        <v>1.7906316355054099</v>
+      </c>
+      <c r="C196" s="2">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A197" s="2">
+        <v>11.8149664367733</v>
+      </c>
+      <c r="B197" s="2">
+        <v>1.79891408278925</v>
+      </c>
+      <c r="C197" s="2">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A198" s="2">
+        <v>14.2577325813564</v>
+      </c>
+      <c r="B198" s="2">
+        <v>1.8324287471046601</v>
+      </c>
+      <c r="C198" s="2">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A199" s="2">
+        <v>16.719305683070001</v>
+      </c>
+      <c r="B199" s="2">
+        <v>1.85369175409971</v>
+      </c>
+      <c r="C199" s="2">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A200" s="2">
+        <v>20.047928269965102</v>
+      </c>
+      <c r="B200" s="2">
+        <v>1.89696082160664</v>
+      </c>
+      <c r="C200" s="2">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A201" s="2">
+        <v>22.917668302133201</v>
+      </c>
+      <c r="B201" s="2">
+        <v>1.91897264132018</v>
+      </c>
+      <c r="C201" s="2">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A202" s="2">
+        <v>26.36562494871</v>
+      </c>
+      <c r="B202" s="2">
+        <v>1.9502189559110199</v>
+      </c>
+      <c r="C202" s="2">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A203" s="2">
+        <v>30.043854087053099</v>
+      </c>
+      <c r="B203" s="2">
+        <v>1.9728487685937399</v>
+      </c>
+      <c r="C203" s="2">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A204" s="2">
+        <v>34.563943348428602</v>
+      </c>
+      <c r="B204" s="2">
+        <v>2.0142462051902998</v>
+      </c>
+      <c r="C204" s="2">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A205" s="2">
+        <v>39.7640787474135</v>
+      </c>
+      <c r="B205" s="2">
+        <v>2.0707971859465801</v>
+      </c>
+      <c r="C205" s="2">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A206" s="2">
+        <v>44.737846746596098</v>
+      </c>
+      <c r="B206" s="2">
+        <v>2.1142499313238399</v>
+      </c>
+      <c r="C206" s="2">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A207" s="2">
+        <v>50.173670602499797</v>
+      </c>
+      <c r="B207" s="2">
+        <v>2.1486759137767999</v>
+      </c>
+      <c r="C207" s="2">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A208" s="2">
+        <v>16.666134512253102</v>
+      </c>
+      <c r="B208" s="2">
+        <v>9.9898526603189506</v>
+      </c>
+      <c r="C208" s="2">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A209" s="2">
+        <v>15.7374543838975</v>
+      </c>
+      <c r="B209" s="2">
+        <v>8.94250177022505</v>
+      </c>
+      <c r="C209" s="2">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A210" s="2">
+        <v>14.6723833022682</v>
+      </c>
+      <c r="B210" s="2">
+        <v>8.0049566925169202</v>
+      </c>
+      <c r="C210" s="2">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A211" s="2">
+        <v>13.5492974598725</v>
+      </c>
+      <c r="B211" s="2">
+        <v>7.0184333427186996</v>
+      </c>
+      <c r="C211" s="2">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A212" s="2">
+        <v>12.314481009164201</v>
+      </c>
+      <c r="B212" s="2">
+        <v>5.9854438421240399</v>
+      </c>
+      <c r="C212" s="2">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A213" s="2">
+        <v>11.050502507200701</v>
+      </c>
+      <c r="B213" s="2">
+        <v>4.99958299541077</v>
+      </c>
+      <c r="C213" s="2">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A214" s="2">
+        <v>9.9478973911185999</v>
+      </c>
+      <c r="B214" s="2">
+        <v>4.27358205896941</v>
+      </c>
+      <c r="C214" s="2">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A215" s="2">
+        <v>9.4235438135936302</v>
+      </c>
+      <c r="B215" s="2">
+        <v>3.8610047569815</v>
+      </c>
+      <c r="C215" s="2">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A216" s="2">
+        <v>8.9838795817379609</v>
+      </c>
+      <c r="B216" s="2">
+        <v>3.60278052631935</v>
+      </c>
+      <c r="C216" s="2">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A217" s="2">
+        <v>8.4832745712020294</v>
+      </c>
+      <c r="B217" s="2">
+        <v>3.2700189132128599</v>
+      </c>
+      <c r="C217" s="2">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A218" s="2">
+        <v>8.0617594658276293</v>
+      </c>
+      <c r="B218" s="2">
+        <v>3.0093675140373999</v>
+      </c>
+      <c r="C218" s="2">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A219" s="2">
+        <v>7.6856305537048604</v>
+      </c>
+      <c r="B219" s="2">
+        <v>2.7440489547251099</v>
+      </c>
+      <c r="C219" s="2">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A220" s="2">
+        <v>7.3270502870278298</v>
+      </c>
+      <c r="B220" s="2">
+        <v>2.5546254865765801</v>
+      </c>
+      <c r="C220" s="2">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A221" s="2">
+        <v>7.11998326723399</v>
+      </c>
+      <c r="B221" s="2">
+        <v>2.34017338578641</v>
+      </c>
+      <c r="C221" s="2">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A222" s="2">
+        <v>6.9408415356047897</v>
+      </c>
+      <c r="B222" s="2">
+        <v>2.1836624488164298</v>
+      </c>
+      <c r="C222" s="2">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A223" s="2">
+        <v>7.2805210398121796</v>
+      </c>
+      <c r="B223" s="2">
+        <v>2.08037552031087</v>
+      </c>
+      <c r="C223" s="2">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A224" s="2">
+        <v>7.7594255514789499</v>
+      </c>
+      <c r="B224" s="2">
+        <v>2.0235629667622401</v>
+      </c>
+      <c r="C224" s="2">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A225" s="2">
+        <v>8.3758733496030402</v>
+      </c>
+      <c r="B225" s="2">
+        <v>2.0003514304202099</v>
+      </c>
+      <c r="C225" s="2">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A226" s="2">
+        <v>9.1864435433416407</v>
+      </c>
+      <c r="B226" s="2">
+        <v>2.0003514304202099</v>
+      </c>
+      <c r="C226" s="2">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A227" s="2">
+        <v>10.139847650294101</v>
+      </c>
+      <c r="B227" s="2">
+        <v>2.0003514304202099</v>
+      </c>
+      <c r="C227" s="2">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A228" s="2">
+        <v>11.702601749965201</v>
+      </c>
+      <c r="B228" s="2">
+        <v>2.0188992116409499</v>
+      </c>
+      <c r="C228" s="2">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A229" s="2">
+        <v>13.6793935357774</v>
+      </c>
+      <c r="B229" s="2">
+        <v>2.0235629667622401</v>
+      </c>
+      <c r="C229" s="2">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A230" s="2">
+        <v>16.092294525793399</v>
+      </c>
+      <c r="B230" s="2">
+        <v>2.0423259714138799</v>
+      </c>
+      <c r="C230" s="2">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A231" s="2">
+        <v>19.984171327016998</v>
+      </c>
+      <c r="B231" s="2">
+        <v>2.0899981586223602</v>
+      </c>
+      <c r="C231" s="2">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A232" s="2">
+        <v>9.2157517166606606</v>
+      </c>
+      <c r="B232" s="2">
+        <v>3.22505970106215</v>
+      </c>
+      <c r="C232" s="2">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A233" s="2">
+        <v>24.581266182867498</v>
+      </c>
+      <c r="B233" s="2">
+        <v>2.1289358640837799</v>
+      </c>
+      <c r="C233" s="2">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A234" s="2">
+        <v>30.043854087053099</v>
+      </c>
+      <c r="B234" s="2">
+        <v>2.1836624488164298</v>
+      </c>
+      <c r="C234" s="2">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A235" s="2">
+        <v>34.454022196753797</v>
+      </c>
+      <c r="B235" s="2">
+        <v>2.2243451666017999</v>
+      </c>
+      <c r="C235" s="2">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A236" s="2">
+        <v>40.402450097293602</v>
+      </c>
+      <c r="B236" s="2">
+        <v>2.27101989883122</v>
+      </c>
+      <c r="C236" s="2">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A237" s="2">
+        <v>45.167405424704903</v>
+      </c>
+      <c r="B237" s="2">
+        <v>2.3240302836995599</v>
+      </c>
+      <c r="C237" s="2">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A238" s="2">
+        <v>50.3337432821099</v>
+      </c>
+      <c r="B238" s="2">
+        <v>2.3727967668935501</v>
+      </c>
+      <c r="C238" s="2">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A239" s="2">
+        <v>18.278989830929898</v>
+      </c>
+      <c r="B239" s="2">
+        <v>9.9209401548150193</v>
+      </c>
+      <c r="C239" s="2">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A240" s="2">
+        <v>17.096284110219699</v>
+      </c>
+      <c r="B240" s="2">
+        <v>8.9838647161425609</v>
+      </c>
+      <c r="C240" s="2">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A241" s="2">
+        <v>16.092294525793399</v>
+      </c>
+      <c r="B241" s="2">
+        <v>8.0049566925169202</v>
+      </c>
+      <c r="C241" s="2">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A242" s="2">
+        <v>14.9079333119673</v>
+      </c>
+      <c r="B242" s="2">
+        <v>6.9861195125405802</v>
+      </c>
+      <c r="C242" s="2">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A243" s="2">
+        <v>13.6793935357774</v>
+      </c>
+      <c r="B243" s="2">
+        <v>5.95788603735331</v>
+      </c>
+      <c r="C243" s="2">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A244" s="2">
+        <v>12.4723857730662</v>
+      </c>
+      <c r="B244" s="2">
+        <v>5.0111322746738001</v>
+      </c>
+      <c r="C244" s="2">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A245" s="2">
+        <v>11.777392173193601</v>
+      </c>
+      <c r="B245" s="2">
+        <v>4.4548138939575903</v>
+      </c>
+      <c r="C245" s="2">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A246" s="2">
+        <v>11.121125414572701</v>
+      </c>
+      <c r="B246" s="2">
+        <v>3.9877646335043102</v>
+      </c>
+      <c r="C246" s="2">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A247" s="2">
+        <v>10.468030624421401</v>
+      </c>
+      <c r="B247" s="2">
+        <v>3.59447710981763</v>
+      </c>
+      <c r="C247" s="2">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="248" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A248" s="2">
+        <v>9.9796348855606105</v>
+      </c>
+      <c r="B248" s="2">
+        <v>3.2624824205493299</v>
+      </c>
+      <c r="C248" s="2">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="249" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A249" s="2">
+        <v>9.5443789880437695</v>
+      </c>
+      <c r="B249" s="2">
+        <v>3.0093675140373999</v>
+      </c>
+      <c r="C249" s="2">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A250" s="2">
+        <v>9.1864435433416407</v>
+      </c>
+      <c r="B250" s="2">
+        <v>2.76949249374392</v>
+      </c>
+      <c r="C250" s="2">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="251" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A251" s="2">
+        <v>9.01254150064233</v>
+      </c>
+      <c r="B251" s="2">
+        <v>2.6629607094063799</v>
+      </c>
+      <c r="C251" s="2">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="252" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A252" s="2">
+        <v>9.0701399567461696</v>
+      </c>
+      <c r="B252" s="2">
+        <v>2.5253223300670502</v>
+      </c>
+      <c r="C252" s="2">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="253" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A253" s="2">
+        <v>9.5443789880437695</v>
+      </c>
+      <c r="B253" s="2">
+        <v>2.4114326247698199</v>
+      </c>
+      <c r="C253" s="2">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="254" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A254" s="2">
+        <v>10.172197537490501</v>
+      </c>
+      <c r="B254" s="2">
+        <v>2.3347799308794399</v>
+      </c>
+      <c r="C254" s="2">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="255" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A255" s="2">
+        <v>11.2637281504578</v>
+      </c>
+      <c r="B255" s="2">
+        <v>2.3026792400199798</v>
+      </c>
+      <c r="C255" s="2">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="256" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A256" s="2">
+        <v>12.7536068034523</v>
+      </c>
+      <c r="B256" s="2">
+        <v>2.2973721987888802</v>
+      </c>
+      <c r="C256" s="2">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="257" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A257" s="2">
+        <v>14.719193664820001</v>
+      </c>
+      <c r="B257" s="2">
+        <v>2.2815243500090401</v>
+      </c>
+      <c r="C257" s="2">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="258" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A258" s="2">
+        <v>16.7726464897077</v>
+      </c>
+      <c r="B258" s="2">
+        <v>2.3026792400199798</v>
+      </c>
+      <c r="C258" s="2">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="259" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A259" s="2">
+        <v>19.984171327016998</v>
+      </c>
+      <c r="B259" s="2">
+        <v>2.3240302836995599</v>
+      </c>
+      <c r="C259" s="2">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="260" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A260" s="2">
+        <v>22.990784192031001</v>
+      </c>
+      <c r="B260" s="2">
+        <v>2.35099770180905</v>
+      </c>
+      <c r="C260" s="2">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="261" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A261" s="2">
+        <v>26.36562494871</v>
+      </c>
+      <c r="B261" s="2">
+        <v>2.3947979586063401</v>
+      </c>
+      <c r="C261" s="2">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="262" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A262" s="2">
+        <v>30.043854087053099</v>
+      </c>
+      <c r="B262" s="2">
+        <v>2.4281828380997701</v>
+      </c>
+      <c r="C262" s="2">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="263" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A263" s="2">
+        <v>34.784838838739297</v>
+      </c>
+      <c r="B263" s="2">
+        <v>2.4963552991406699</v>
+      </c>
+      <c r="C263" s="2">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="264" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A264" s="2">
+        <v>40.273961174591399</v>
+      </c>
+      <c r="B264" s="2">
+        <v>2.5842686689795298</v>
+      </c>
+      <c r="C264" s="2">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="265" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A265" s="2">
+        <v>44.880577125352801</v>
+      </c>
+      <c r="B265" s="2">
+        <v>2.6691122778327099</v>
+      </c>
+      <c r="C265" s="2">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="266" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A266" s="2">
+        <v>50.3337432821099</v>
+      </c>
+      <c r="B266" s="2">
+        <v>2.7440489547251099</v>
+      </c>
+      <c r="C266" s="2">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="267" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A267" s="2">
+        <v>21.029058627169501</v>
+      </c>
+      <c r="B267" s="2">
+        <v>9.9668288022672193</v>
+      </c>
+      <c r="C267" s="2">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="268" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A268" s="2">
+        <v>19.984171327016998</v>
+      </c>
+      <c r="B268" s="2">
+        <v>9.1723783903273297</v>
+      </c>
+      <c r="C268" s="2">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="269" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A269" s="2">
+        <v>18.750766902045601</v>
+      </c>
+      <c r="B269" s="2">
+        <v>8.2296998995324895</v>
+      </c>
+      <c r="C269" s="2">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="270" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A270" s="2">
+        <v>17.593487048398401</v>
+      </c>
+      <c r="B270" s="2">
+        <v>7.4351937138859503</v>
+      </c>
+      <c r="C270" s="2">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="271" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A271" s="2">
+        <v>16.298641018661801</v>
+      </c>
+      <c r="B271" s="2">
+        <v>6.5188874188277603</v>
+      </c>
+      <c r="C271" s="2">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="272" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A272" s="2">
+        <v>15.051074580323199</v>
+      </c>
+      <c r="B272" s="2">
+        <v>5.7155058515806596</v>
+      </c>
+      <c r="C272" s="2">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="273" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A273" s="2">
+        <v>14.167191157724099</v>
+      </c>
+      <c r="B273" s="2">
+        <v>5.0927277138891602</v>
+      </c>
+      <c r="C273" s="2">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="274" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A274" s="2">
+        <v>13.4632548388433</v>
+      </c>
+      <c r="B274" s="2">
+        <v>4.6330287926373197</v>
+      </c>
+      <c r="C274" s="2">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="275" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A275" s="2">
+        <v>12.672617087181401</v>
+      </c>
+      <c r="B275" s="2">
+        <v>4.0808474541767499</v>
+      </c>
+      <c r="C275" s="2">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="276" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A276" s="2">
+        <v>12.081364309304</v>
+      </c>
+      <c r="B276" s="2">
+        <v>3.6445862159833098</v>
+      </c>
+      <c r="C276" s="2">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="277" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A277" s="2">
+        <v>11.7399374042642</v>
+      </c>
+      <c r="B277" s="2">
+        <v>3.3618263477545201</v>
+      </c>
+      <c r="C277" s="2">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="278" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A278" s="2">
+        <v>11.6282862712173</v>
+      </c>
+      <c r="B278" s="2">
+        <v>3.1297573079481502</v>
+      </c>
+      <c r="C278" s="2">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="279" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A279" s="2">
+        <v>11.852660576235801</v>
+      </c>
+      <c r="B279" s="2">
+        <v>2.9407248069056</v>
+      </c>
+      <c r="C279" s="2">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="280" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A280" s="2">
+        <v>12.512177324847199</v>
+      </c>
+      <c r="B280" s="2">
+        <v>2.84068527516223</v>
+      </c>
+      <c r="C280" s="2">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="281" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A281" s="2">
+        <v>13.592524760669701</v>
+      </c>
+      <c r="B281" s="2">
+        <v>2.7440489547251099</v>
+      </c>
+      <c r="C281" s="2">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="282" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A282" s="2">
+        <v>14.8605227146803</v>
+      </c>
+      <c r="B282" s="2">
+        <v>2.7188391674421299</v>
+      </c>
+      <c r="C282" s="2">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="283" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A283" s="2">
+        <v>16.719305683070001</v>
+      </c>
+      <c r="B283" s="2">
+        <v>2.6938609843999499</v>
+      </c>
+      <c r="C283" s="2">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="284" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A284" s="2">
+        <v>19.1735496867243</v>
+      </c>
+      <c r="B284" s="2">
+        <v>2.7125729922356299</v>
+      </c>
+      <c r="C284" s="2">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="285" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A285" s="2">
+        <v>22.699712827192101</v>
+      </c>
+      <c r="B285" s="2">
+        <v>2.75674137027343</v>
+      </c>
+      <c r="C285" s="2">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="286" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A286" s="2">
+        <v>26.198194313846599</v>
+      </c>
+      <c r="B286" s="2">
+        <v>2.8081008334701698</v>
+      </c>
+      <c r="C286" s="2">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="287" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A287" s="2">
+        <v>29.948307840818799</v>
+      </c>
+      <c r="B287" s="2">
+        <v>2.8604171490174002</v>
+      </c>
+      <c r="C287" s="2">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="288" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A288" s="2">
+        <v>35.007146055054498</v>
+      </c>
+      <c r="B288" s="2">
+        <v>2.9611515720386499</v>
+      </c>
+      <c r="C288" s="2">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="289" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A289" s="2">
+        <v>40.0182079011133</v>
+      </c>
+      <c r="B289" s="2">
+        <v>3.1081674582232699</v>
+      </c>
+      <c r="C289" s="2">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="290" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A290" s="2">
+        <v>44.595570282702397</v>
+      </c>
+      <c r="B290" s="2">
+        <v>3.21021108365631</v>
+      </c>
+      <c r="C290" s="2">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="291" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A291" s="2">
+        <v>50.3337432821099</v>
+      </c>
+      <c r="B291" s="2">
+        <v>3.33863562767382</v>
+      </c>
+      <c r="C291" s="2">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="292" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A292" s="2">
+        <v>24.659689569054901</v>
+      </c>
+      <c r="B292" s="2">
+        <v>9.9898526603189506</v>
+      </c>
+      <c r="C292" s="2">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="293" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A293" s="2">
+        <v>22.990784192031001</v>
+      </c>
+      <c r="B293" s="2">
+        <v>8.9218917674166196</v>
+      </c>
+      <c r="C293" s="2">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="294" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A294" s="2">
+        <v>21.503211178476398</v>
+      </c>
+      <c r="B294" s="2">
+        <v>7.9681007734657596</v>
+      </c>
+      <c r="C294" s="2">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="295" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A295" s="2">
+        <v>19.984171327016998</v>
+      </c>
+      <c r="B295" s="2">
+        <v>7.1491902475379501</v>
+      </c>
+      <c r="C295" s="2">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="296" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A296" s="2">
+        <v>18.572440195691001</v>
+      </c>
+      <c r="B296" s="2">
+        <v>6.3555121476715204</v>
+      </c>
+      <c r="C296" s="2">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="297" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A297" s="2">
+        <v>17.370747352149699</v>
+      </c>
+      <c r="B297" s="2">
+        <v>5.6499454148825698</v>
+      </c>
+      <c r="C297" s="2">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="298" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A298" s="2">
+        <v>16.350639748484301</v>
+      </c>
+      <c r="B298" s="2">
+        <v>4.98806033405448</v>
+      </c>
+      <c r="C298" s="2">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="299" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A299" s="2">
+        <v>15.8885604516579</v>
+      </c>
+      <c r="B299" s="2">
+        <v>4.59046480334072</v>
+      </c>
+      <c r="C299" s="2">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="300" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A300" s="2">
+        <v>15.990103013394</v>
+      </c>
+      <c r="B300" s="2">
+        <v>4.2051109321558799</v>
+      </c>
+      <c r="C300" s="2">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="301" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A301" s="2">
+        <v>16.507633428497002</v>
+      </c>
+      <c r="B301" s="2">
+        <v>3.8878239401853301</v>
+      </c>
+      <c r="C301" s="2">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="302" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A302" s="2">
+        <v>17.819082866567399</v>
+      </c>
+      <c r="B302" s="2">
+        <v>3.6699021198945498</v>
+      </c>
+      <c r="C302" s="2">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="303" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A303" s="2">
+        <v>19.1735496867243</v>
+      </c>
+      <c r="B303" s="2">
+        <v>3.5287350208467498</v>
+      </c>
+      <c r="C303" s="2">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="304" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A304" s="2">
+        <v>21.5718144238086</v>
+      </c>
+      <c r="B304" s="2">
+        <v>3.4562113224452702</v>
+      </c>
+      <c r="C304" s="2">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="305" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A305" s="2">
+        <v>24.503092200772699</v>
+      </c>
+      <c r="B305" s="2">
+        <v>3.4721977975596299</v>
+      </c>
+      <c r="C305" s="2">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="306" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A306" s="2">
+        <v>27.567986439700601</v>
+      </c>
+      <c r="B306" s="2">
+        <v>3.5206022588346699</v>
+      </c>
+      <c r="C306" s="2">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="307" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A307" s="2">
+        <v>31.614719401881398</v>
+      </c>
+      <c r="B307" s="2">
+        <v>3.62780604093542</v>
+      </c>
+      <c r="C307" s="2">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="308" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A308" s="2">
+        <v>36.025241903462799</v>
+      </c>
+      <c r="B308" s="2">
+        <v>3.7903879438831001</v>
+      </c>
+      <c r="C308" s="2">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="309" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A309" s="2">
+        <v>40.790381665713902</v>
+      </c>
+      <c r="B309" s="2">
+        <v>3.96940441793127</v>
+      </c>
+      <c r="C309" s="2">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="310" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A310" s="2">
+        <v>45.456066821547701</v>
+      </c>
+      <c r="B310" s="2">
+        <v>4.1186861382320696</v>
+      </c>
+      <c r="C310" s="2">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="311" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A311" s="2">
+        <v>50.014106990189099</v>
+      </c>
+      <c r="B311" s="2">
+        <v>4.27358205896941</v>
+      </c>
+      <c r="C311" s="2">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="312" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A312" s="2">
+        <v>33.267718581099402</v>
+      </c>
+      <c r="B312" s="2">
+        <v>9.9898526603189506</v>
+      </c>
+      <c r="C312" s="2">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="313" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A313" s="2">
+        <v>31.614719401881398</v>
+      </c>
+      <c r="B313" s="2">
+        <v>9.0046178794690306</v>
+      </c>
+      <c r="C313" s="2">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="314" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A314" s="2">
+        <v>30.332325687396999</v>
+      </c>
+      <c r="B314" s="2">
+        <v>8.2296998995324895</v>
+      </c>
+      <c r="C314" s="2">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="315" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A315" s="2">
+        <v>29.194795996112902</v>
+      </c>
+      <c r="B315" s="2">
+        <v>7.5737150717567703</v>
+      </c>
+      <c r="C315" s="2">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="316" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A316" s="2">
+        <v>28.460242821897801</v>
+      </c>
+      <c r="B316" s="2">
+        <v>7.0998733427712697</v>
+      </c>
+      <c r="C316" s="2">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="317" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A317" s="2">
+        <v>27.567986439700601</v>
+      </c>
+      <c r="B317" s="2">
+        <v>6.6097645093675697</v>
+      </c>
+      <c r="C317" s="2">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="318" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A318" s="2">
+        <v>27.3058047247712</v>
+      </c>
+      <c r="B318" s="2">
+        <v>6.1393061097079</v>
+      </c>
+      <c r="C318" s="2">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="319" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A319" s="2">
+        <v>28.2795106551728</v>
+      </c>
+      <c r="B319" s="2">
+        <v>5.7951833347742996</v>
+      </c>
+      <c r="C319" s="2">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="320" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A320" s="2">
+        <v>29.475115208764802</v>
+      </c>
+      <c r="B320" s="2">
+        <v>5.5338259174329201</v>
+      </c>
+      <c r="C320" s="2">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="321" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A321" s="2">
+        <v>30.819279951245601</v>
+      </c>
+      <c r="B321" s="2">
+        <v>5.3702981375180396</v>
+      </c>
+      <c r="C321" s="2">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="322" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A322" s="2">
+        <v>33.801797556069403</v>
+      </c>
+      <c r="B322" s="2">
+        <v>5.4076011243503697</v>
+      </c>
+      <c r="C322" s="2">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="323" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A323" s="2">
+        <v>37.788289834458801</v>
+      </c>
+      <c r="B323" s="2">
+        <v>5.4577418151600803</v>
+      </c>
+      <c r="C323" s="2">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="324" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A324" s="2">
+        <v>40.273961174591399</v>
+      </c>
+      <c r="B324" s="2">
+        <v>5.5338259174329201</v>
+      </c>
+      <c r="C324" s="2">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="325" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A325" s="2">
+        <v>43.473527240803698</v>
+      </c>
+      <c r="B325" s="2">
+        <v>5.7287089473728399</v>
+      </c>
+      <c r="C325" s="2">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="326" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A326" s="2">
+        <v>46.333167123696697</v>
+      </c>
+      <c r="B326" s="2">
+        <v>5.9031504833832296</v>
+      </c>
+      <c r="C326" s="2">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="327" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A327" s="2">
+        <v>50.014106990189099</v>
+      </c>
+      <c r="B327" s="2">
+        <v>6.1534882046560799</v>
+      </c>
+      <c r="C327" s="2">
+        <v>0.8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>